--- a/data/trans_bre/P12_2_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P12_2_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 14,72</t>
+          <t>2,96; 15,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 11,97</t>
+          <t>0,24; 12,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 5,65</t>
+          <t>-4,64; 5,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 5,96</t>
+          <t>-3,04; 5,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,17; 96,78</t>
+          <t>15,03; 102,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 93,02</t>
+          <t>0,65; 96,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-31,29; 51,32</t>
+          <t>-30,29; 50,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 43,14</t>
+          <t>-16,48; 44,0</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 14,32</t>
+          <t>2,22; 14,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 12,05</t>
+          <t>-0,51; 11,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 14,1</t>
+          <t>4,14; 13,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,07; 12,22</t>
+          <t>2,85; 12,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,25; 104,18</t>
+          <t>11,18; 104,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 85,65</t>
+          <t>-3,5; 81,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,66; 220,04</t>
+          <t>38,37; 230,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,19; 108,38</t>
+          <t>16,46; 103,36</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 17,43</t>
+          <t>1,22; 16,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 11,04</t>
+          <t>-1,47; 11,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 12,21</t>
+          <t>-2,47; 11,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,04; 25,49</t>
+          <t>7,34; 26,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 95,38</t>
+          <t>4,93; 94,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 60,9</t>
+          <t>-7,14; 65,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 79,1</t>
+          <t>-13,94; 77,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36,39; 613,69</t>
+          <t>39,16; 645,37</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 4,52</t>
+          <t>-3,32; 4,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 6,32</t>
+          <t>-1,97; 6,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 4,17</t>
+          <t>-2,91; 4,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 3,99</t>
+          <t>-10,11; 4,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 21,0</t>
+          <t>-13,34; 20,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 35,45</t>
+          <t>-9,57; 33,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,63; 26,38</t>
+          <t>-15,14; 26,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,75; 21,27</t>
+          <t>-48,3; 22,45</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,87; 17,12</t>
+          <t>5,13; 17,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,46; 18,6</t>
+          <t>7,79; 17,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 12,84</t>
+          <t>3,72; 12,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 9,21</t>
+          <t>-3,15; 9,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,91; 93,55</t>
+          <t>20,94; 98,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,43; 120,17</t>
+          <t>38,09; 117,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,82; 69,88</t>
+          <t>16,0; 69,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 47,34</t>
+          <t>-12,7; 53,44</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,91; 30,65</t>
+          <t>22,94; 30,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,66; 24,29</t>
+          <t>15,37; 24,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,98; 22,3</t>
+          <t>13,59; 21,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,47; 21,26</t>
+          <t>12,16; 21,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>227,62; 657,68</t>
+          <t>230,95; 687,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>145,44; 533,19</t>
+          <t>137,57; 517,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>118,75; 487,38</t>
+          <t>126,25; 443,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>83,04; 848,32</t>
+          <t>101,19; 821,23</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,07; 12,04</t>
+          <t>8,09; 12,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,1; 10,06</t>
+          <t>5,99; 10,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,37</t>
+          <t>4,69; 8,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 9,25</t>
+          <t>1,84; 9,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>39,35; 65,97</t>
+          <t>39,61; 67,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,61; 62,64</t>
+          <t>32,98; 62,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,47; 56,42</t>
+          <t>28,57; 57,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,59; 73,63</t>
+          <t>12,54; 71,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P12_2_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P12_2_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>2,24</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 15,43</t>
+          <t>2,62; 15,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 12,22</t>
+          <t>0,29; 11,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 5,52</t>
+          <t>-4,44; 5,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 5,92</t>
+          <t>-2,2; 6,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,03; 102,92</t>
+          <t>14,1; 102,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 96,53</t>
+          <t>1,66; 94,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 50,49</t>
+          <t>-29,38; 54,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 44,0</t>
+          <t>-12,14; 48,26</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,7</t>
+          <t>7,83</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>57,96%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 14,44</t>
+          <t>2,47; 14,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 11,7</t>
+          <t>-1,04; 11,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 13,92</t>
+          <t>3,99; 13,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 12,27</t>
+          <t>3,33; 12,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,18; 104,81</t>
+          <t>11,73; 101,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 81,62</t>
+          <t>-7,72; 81,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,37; 230,85</t>
+          <t>34,83; 225,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,46; 103,36</t>
+          <t>20,38; 107,94</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,28</t>
+          <t>8,44</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>139,65%</t>
+          <t>48,98%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 16,94</t>
+          <t>1,98; 16,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 11,32</t>
+          <t>-2,12; 10,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 11,92</t>
+          <t>-3,64; 12,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 26,73</t>
+          <t>2,51; 15,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 94,9</t>
+          <t>7,25; 96,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 65,35</t>
+          <t>-10,48; 56,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 77,66</t>
+          <t>-19,0; 76,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,16; 645,37</t>
+          <t>11,87; 100,56</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,75</t>
+          <t>4,02</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-9,1%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 4,62</t>
+          <t>-3,41; 4,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 6,01</t>
+          <t>-1,95; 6,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 4,29</t>
+          <t>-2,67; 4,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 4,26</t>
+          <t>1,1; 7,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 20,93</t>
+          <t>-13,75; 20,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 33,71</t>
+          <t>-9,47; 35,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 26,74</t>
+          <t>-14,03; 27,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,3; 22,45</t>
+          <t>5,15; 42,9</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,17</t>
+          <t>7,63</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,13; 17,05</t>
+          <t>4,84; 16,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 17,72</t>
+          <t>7,7; 17,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,72; 12,81</t>
+          <t>3,23; 12,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 9,85</t>
+          <t>2,92; 11,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,94; 98,87</t>
+          <t>19,45; 93,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,09; 117,24</t>
+          <t>37,59; 116,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,0; 69,25</t>
+          <t>14,84; 69,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 53,44</t>
+          <t>12,36; 65,34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17,86</t>
+          <t>17,19</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>363,15%</t>
+          <t>317,13%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,94; 30,4</t>
+          <t>22,99; 30,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,37; 24,11</t>
+          <t>15,19; 24,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,59; 21,92</t>
+          <t>13,87; 22,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,16; 21,61</t>
+          <t>10,89; 20,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>230,95; 687,0</t>
+          <t>235,02; 694,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>137,57; 517,14</t>
+          <t>136,66; 518,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>126,25; 443,49</t>
+          <t>125,87; 447,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>101,19; 821,23</t>
+          <t>97,7; 820,87</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,68</t>
+          <t>6,56</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>39,06%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,09; 12,31</t>
+          <t>8,04; 12,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,99; 10,1</t>
+          <t>6,22; 10,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,69; 8,43</t>
+          <t>4,6; 8,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 9,19</t>
+          <t>4,9; 8,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>39,61; 67,1</t>
+          <t>38,9; 65,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,98; 62,55</t>
+          <t>34,17; 63,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,57; 57,27</t>
+          <t>27,82; 58,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,54; 71,2</t>
+          <t>27,62; 52,85</t>
         </is>
       </c>
     </row>
